--- a/New_Structure/01_Pore_diameters_33_new_structure_stable.xlsx
+++ b/New_Structure/01_Pore_diameters_33_new_structure_stable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python_program\GAIN\DETECTION\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python_program\GAIN\CrystalCGAIN\New_Structure\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F9645B5-4AC9-4BC1-B805-CD504D78F830}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1B13007-2610-4EE1-9E97-7885596F77DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,18 +34,12 @@
     <t>沿自由球体路径的包含球体直径</t>
   </si>
   <si>
-    <t>optimize_8000022_new_stable.cif</t>
-  </si>
-  <si>
     <t>2.39668</t>
   </si>
   <si>
     <t>0.71404</t>
   </si>
   <si>
-    <t>optimize_8000028_new_stable.cif</t>
-  </si>
-  <si>
     <t>3.00126</t>
   </si>
   <si>
@@ -55,18 +49,12 @@
     <t>2.78908</t>
   </si>
   <si>
-    <t>optimize_8000029_new_stable.cif</t>
-  </si>
-  <si>
     <t>2.27416</t>
   </si>
   <si>
     <t>1.29281</t>
   </si>
   <si>
-    <t>optimize_8000067_new_stable.cif</t>
-  </si>
-  <si>
     <t>4.03483</t>
   </si>
   <si>
@@ -76,90 +64,60 @@
     <t>3.78840</t>
   </si>
   <si>
-    <t>optimize_8000220_new_stable.cif</t>
-  </si>
-  <si>
     <t>2.13393</t>
   </si>
   <si>
     <t>1.53630</t>
   </si>
   <si>
-    <t>optimize_8020115_new_stable.cif</t>
-  </si>
-  <si>
     <t>2.42177</t>
   </si>
   <si>
     <t>1.99492</t>
   </si>
   <si>
-    <t>optimize_8036302_new_stable.cif</t>
-  </si>
-  <si>
     <t>2.03706</t>
   </si>
   <si>
     <t>0.83381</t>
   </si>
   <si>
-    <t>optimize_8046024_new_stable.cif</t>
-  </si>
-  <si>
     <t>1.75959</t>
   </si>
   <si>
     <t>1.47907</t>
   </si>
   <si>
-    <t>optimize_9000010_new_stable.cif</t>
-  </si>
-  <si>
     <t>3.85293</t>
   </si>
   <si>
     <t>2.13700</t>
   </si>
   <si>
-    <t>optimize_9000171_new_stable.cif</t>
-  </si>
-  <si>
     <t>2.18811</t>
   </si>
   <si>
     <t>1.19954</t>
   </si>
   <si>
-    <t>optimize_9000182_new_stable.cif</t>
-  </si>
-  <si>
     <t>2.79186</t>
   </si>
   <si>
     <t>1.60952</t>
   </si>
   <si>
-    <t>optimize_9000297_new_stable.cif</t>
-  </si>
-  <si>
     <t>3.51954</t>
   </si>
   <si>
     <t>1.75775</t>
   </si>
   <si>
-    <t>optimize_9000332_new_stable.cif</t>
-  </si>
-  <si>
     <t>2.87573</t>
   </si>
   <si>
     <t>0.95460</t>
   </si>
   <si>
-    <t>optimize_9000347_new_stable.cif</t>
-  </si>
-  <si>
     <t>2.33942</t>
   </si>
   <si>
@@ -169,18 +127,12 @@
     <t>2.27428</t>
   </si>
   <si>
-    <t>optimize_9000483_new_stable.cif</t>
-  </si>
-  <si>
     <t>3.11778</t>
   </si>
   <si>
     <t>0.86971</t>
   </si>
   <si>
-    <t>optimize_9000533_new_stable.cif</t>
-  </si>
-  <si>
     <t>2.99864</t>
   </si>
   <si>
@@ -190,18 +142,12 @@
     <t>2.99622</t>
   </si>
   <si>
-    <t>optimize_9000550_new_stable.cif</t>
-  </si>
-  <si>
     <t>3.52444</t>
   </si>
   <si>
     <t>1.69066</t>
   </si>
   <si>
-    <t>optimize_9000668_new_stable.cif</t>
-  </si>
-  <si>
     <t>3.26727</t>
   </si>
   <si>
@@ -211,18 +157,12 @@
     <t>3.26142</t>
   </si>
   <si>
-    <t>optimize_9000670_new_stable.cif</t>
-  </si>
-  <si>
     <t>3.68027</t>
   </si>
   <si>
     <t>1.50700</t>
   </si>
   <si>
-    <t>optimize_9000682_new_stable.cif</t>
-  </si>
-  <si>
     <t>2.56870</t>
   </si>
   <si>
@@ -232,9 +172,6 @@
     <t>2.52131</t>
   </si>
   <si>
-    <t>optimize_9000703_new_stable.cif</t>
-  </si>
-  <si>
     <t>2.62048</t>
   </si>
   <si>
@@ -244,9 +181,6 @@
     <t>2.59844</t>
   </si>
   <si>
-    <t>optimize_9000765_new_stable.cif</t>
-  </si>
-  <si>
     <t>3.04104</t>
   </si>
   <si>
@@ -256,9 +190,6 @@
     <t>3.00824</t>
   </si>
   <si>
-    <t>optimize_9000805_new_stable.cif</t>
-  </si>
-  <si>
     <t>3.06885</t>
   </si>
   <si>
@@ -268,27 +199,18 @@
     <t>3.04706</t>
   </si>
   <si>
-    <t>optimize_9000806_new_stable.cif</t>
-  </si>
-  <si>
     <t>3.48017</t>
   </si>
   <si>
     <t>2.82173</t>
   </si>
   <si>
-    <t>optimize_9000860_new_stable.cif</t>
-  </si>
-  <si>
     <t>3.36002</t>
   </si>
   <si>
     <t>1.90758</t>
   </si>
   <si>
-    <t>optimize_9000978_new_stable.cif</t>
-  </si>
-  <si>
     <t>2.33802</t>
   </si>
   <si>
@@ -298,9 +220,6 @@
     <t>2.33659</t>
   </si>
   <si>
-    <t>optimize_9033061_new_stable.cif</t>
-  </si>
-  <si>
     <t>2.97807</t>
   </si>
   <si>
@@ -310,36 +229,24 @@
     <t>2.88503</t>
   </si>
   <si>
-    <t>optimize_9058826_new_stable.cif</t>
-  </si>
-  <si>
     <t>2.42315</t>
   </si>
   <si>
     <t>1.33227</t>
   </si>
   <si>
-    <t>optimize_9074698_new_stable.cif</t>
-  </si>
-  <si>
     <t>2.23612</t>
   </si>
   <si>
     <t>1.07412</t>
   </si>
   <si>
-    <t>optimize_9093157_new_stable.cif</t>
-  </si>
-  <si>
     <t>1.73422</t>
   </si>
   <si>
     <t>1.23545</t>
   </si>
   <si>
-    <t>optimize_9104112_new_stable.cif</t>
-  </si>
-  <si>
     <t>2.37654</t>
   </si>
   <si>
@@ -349,9 +256,6 @@
     <t>2.37443</t>
   </si>
   <si>
-    <t>optimize_9119803_new_stable.cif</t>
-  </si>
-  <si>
     <t>2.11764</t>
   </si>
   <si>
@@ -361,13 +265,110 @@
     <t>1.65602</t>
   </si>
   <si>
-    <t>optimize_9311591_new_stable.cif</t>
-  </si>
-  <si>
     <t>1.63933</t>
   </si>
   <si>
     <t>1.43406</t>
+  </si>
+  <si>
+    <t>new_stable_01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>new_stable_02</t>
+  </si>
+  <si>
+    <t>new_stable_03</t>
+  </si>
+  <si>
+    <t>new_stable_04</t>
+  </si>
+  <si>
+    <t>new_stable_05</t>
+  </si>
+  <si>
+    <t>new_stable_06</t>
+  </si>
+  <si>
+    <t>new_stable_07</t>
+  </si>
+  <si>
+    <t>new_stable_08</t>
+  </si>
+  <si>
+    <t>new_stable_09</t>
+  </si>
+  <si>
+    <t>new_stable_10</t>
+  </si>
+  <si>
+    <t>new_stable_11</t>
+  </si>
+  <si>
+    <t>new_stable_12</t>
+  </si>
+  <si>
+    <t>new_stable_13</t>
+  </si>
+  <si>
+    <t>new_stable_14</t>
+  </si>
+  <si>
+    <t>new_stable_15</t>
+  </si>
+  <si>
+    <t>new_stable_16</t>
+  </si>
+  <si>
+    <t>new_stable_17</t>
+  </si>
+  <si>
+    <t>new_stable_18</t>
+  </si>
+  <si>
+    <t>new_stable_19</t>
+  </si>
+  <si>
+    <t>new_stable_20</t>
+  </si>
+  <si>
+    <t>new_stable_21</t>
+  </si>
+  <si>
+    <t>new_stable_22</t>
+  </si>
+  <si>
+    <t>new_stable_23</t>
+  </si>
+  <si>
+    <t>new_stable_24</t>
+  </si>
+  <si>
+    <t>new_stable_25</t>
+  </si>
+  <si>
+    <t>new_stable_26</t>
+  </si>
+  <si>
+    <t>new_stable_27</t>
+  </si>
+  <si>
+    <t>new_stable_28</t>
+  </si>
+  <si>
+    <t>new_stable_29</t>
+  </si>
+  <si>
+    <t>new_stable_30</t>
+  </si>
+  <si>
+    <t>new_stable_31</t>
+  </si>
+  <si>
+    <t>new_stable_32</t>
+  </si>
+  <si>
+    <t>new_stable_33</t>
   </si>
 </sst>
 </file>
@@ -763,464 +764,464 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>91</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="B17" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="D19" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="D20" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="D21" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="D22" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="D23" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="C25" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="C26" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="C27" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="D27" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="D29" t="s">
-        <v>97</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="B30" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="C30" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="D30" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B31" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="C31" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="D31" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="C32" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="D32" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B33" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="D33" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B34" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="C34" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="D34" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
